--- a/data.xlsx
+++ b/data.xlsx
@@ -4,14 +4,15 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="sales" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="my_order" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="order_detail" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="customer" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="profile" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="createCompany" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="createStore" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="validate_msg" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="address" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="ccs3_edit_company" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="my_order" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="order_detail" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="customer" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="profile" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="createCompany" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="createStore" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="validate_msg" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="address" sheetId="10" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="907">
   <si>
     <t>Keyword</t>
   </si>
@@ -560,6 +561,348 @@
     <t>พิมพ์ใบเสร็จ</t>
   </si>
   <si>
+    <t>patona-sellercenter-sales-summary-shippingfee</t>
+  </si>
+  <si>
+    <t>Shipping Fee</t>
+  </si>
+  <si>
+    <t>ค่าจัดส่ง</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-button-editcompany</t>
+  </si>
+  <si>
+    <t>Edit Company</t>
+  </si>
+  <si>
+    <t>แก้ไขบริษัท</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-title-editcompany</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-description-overview</t>
+  </si>
+  <si>
+    <t>Company Overview &amp; Settings</t>
+  </si>
+  <si>
+    <t>ภาพรวมและการตั้งค่าบริษัทของคุณ</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-title-updatelogo</t>
+  </si>
+  <si>
+    <t>Upload Company Logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อัปโหลดโลโก้บริษัท	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-description-recommended</t>
+  </si>
+  <si>
+    <t>Recommended image size: 300px × 300px</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขนาดรูปภาพแนะนำ: ความกว้าง 300px ความสูง 300px	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-description-maxfile</t>
+  </si>
+  <si>
+    <t>Max file size: 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขนาดไฟล์ไม่เกิน: 1MB	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-description-supported</t>
+  </si>
+  <si>
+    <t>Supported formats: JPG, PNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รองรับไฟล์: JPG, PNG	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-title-companyname</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>ชื่อบริษัท</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-label-address-country</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>ประเทศ</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-label-address-postalcode</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>รหัสไปรษณีย์</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-button-cancel</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-button-save</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>บันทึก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-companyname </t>
+  </si>
+  <si>
+    <t>Enter Company Name</t>
+  </si>
+  <si>
+    <t>ระบุชื่อบริษัท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-taxidentification </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter Tax ID </t>
+  </si>
+  <si>
+    <t>ระบุเลขประจำตัวผู้เสียภาษี</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-email </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter Company Email </t>
+  </si>
+  <si>
+    <t>ระบุอีเมลบริษัท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-primaryphone </t>
+  </si>
+  <si>
+    <t>Enter Primary Phone Number</t>
+  </si>
+  <si>
+    <t>ระบุเบอร์โทรศํพท์</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-secondaryphone </t>
+  </si>
+  <si>
+    <t>Enter Secondary Phone Number</t>
+  </si>
+  <si>
+    <t>ระบุเบอร์โทรสำรอง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccs3-mycompany-placeholder-address-postalcode </t>
+  </si>
+  <si>
+    <t>Enter Postal Code</t>
+  </si>
+  <si>
+    <t>ระบุรหัสไปรษณีย์</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-placeholder-address</t>
+  </si>
+  <si>
+    <t>Enter Addres</t>
+  </si>
+  <si>
+    <t>ระบุที่อยู่</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-title-image</t>
+  </si>
+  <si>
+    <t>Upload or Edit Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อัปโหลดหรือแก้ไขรูปภาพ	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-button-cancel</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-title-unsaved</t>
+  </si>
+  <si>
+    <t>You haven’t saved your data yet</t>
+  </si>
+  <si>
+    <t>คุณยังไม่ได้บันทึกข้อมูล</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-button-save</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-toast-update-successfully</t>
+  </si>
+  <si>
+    <t>Saved successfully. Your data has been successfully saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บันทึกข้อมูลสำเร็จ ระบบได้ทำการบันทึกข้อมูลของคุณสำเร็จแล้ว	</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-toast-update-error</t>
+  </si>
+  <si>
+    <t>An error occurred. Please refresh or try again.</t>
+  </si>
+  <si>
+    <t>เกิดข้อผิดพลาด กรุณารีเฟรชหรือลองใหม่อีกครั้ง</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-title-unsaved-warning</t>
+  </si>
+  <si>
+    <t>You have not saved the data</t>
+  </si>
+  <si>
+    <t>คุณไม่ได้ทำการบันทึกข้อมูล</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-title-unsaved-confirm</t>
+  </si>
+  <si>
+    <t>Do you want to leave this page?</t>
+  </si>
+  <si>
+    <t>ต้องการออกจากหน้านี้หรือไม่?</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-modal-button-exit</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>ออก</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-companyname</t>
+  </si>
+  <si>
+    <t>Please enter the company name</t>
+  </si>
+  <si>
+    <t>กรุณาระบุชื่อบริษัท</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-error-mincharacters</t>
+  </si>
+  <si>
+    <t>Please enter more than 2 characters</t>
+  </si>
+  <si>
+    <t>กรุณาระบุมากกว่า 2 ตัวอักษรขึ้นไป</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-error-invalidformat</t>
+  </si>
+  <si>
+    <t>Invalid format</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-error-phone</t>
+  </si>
+  <si>
+    <t>Please enter a valid phone number.</t>
+  </si>
+  <si>
+    <t>กรุณาระบุเบอร์โทรให้ถูกต้อง</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-phone</t>
+  </si>
+  <si>
+    <t>Please enter the primary phone number.</t>
+  </si>
+  <si>
+    <t>กรุณาระบุเบอร์โทรหลัก</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-postalcode</t>
+  </si>
+  <si>
+    <t>Please select or enter the postal code</t>
+  </si>
+  <si>
+    <t>กรุณาเลือกหรือระบุรหัสไปรษณีย์</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-input-address</t>
+  </si>
+  <si>
+    <t>Please enter the address.</t>
+  </si>
+  <si>
+    <t>กรุณาระบุที่อยู่</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-toast-image-deleted</t>
+  </si>
+  <si>
+    <t>Image deleted successfully</t>
+  </si>
+  <si>
+    <t>ลบรูปสำเร็จ</t>
+  </si>
+  <si>
+    <t>sellsuki-topbar-option-settings</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>ตั้งค่า</t>
+  </si>
+  <si>
+    <t>sellsuki-topbar-option-language</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>ภาษา</t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-edit-label-address</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ที่อยู่  </t>
+  </si>
+  <si>
+    <t>ccs3-mycompany-placeholder</t>
+  </si>
+  <si>
+    <t>Enter</t>
+  </si>
+  <si>
+    <t>ระบุ</t>
+  </si>
+  <si>
     <t>patona-sellercenter-myorder-title-myorder</t>
   </si>
   <si>
@@ -1112,6 +1455,9 @@
     <t>patona-sellercenter-orderdetail-badge-deliverystatus-canceled</t>
   </si>
   <si>
+    <t>patona-sellercenter-orderdetail-summary-shippingfee</t>
+  </si>
+  <si>
     <t>patona-sellercenter-customerbook-title-customerbook</t>
   </si>
   <si>
@@ -1352,21 +1698,9 @@
     <t>patona-sellercenter-customerbook-button-save</t>
   </si>
   <si>
-    <t>Save</t>
-  </si>
-  <si>
-    <t>บันทึก</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-button-leave</t>
   </si>
   <si>
-    <t>Leave</t>
-  </si>
-  <si>
-    <t>ออก</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-button-delete</t>
   </si>
   <si>
@@ -1508,18 +1842,9 @@
     <t>patona-sellercenter-customerbook-modal-taxinvoice-label-companyname</t>
   </si>
   <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>ชื่อบริษัท</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-modal-taxinvoice-placeholder-companyname</t>
   </si>
   <si>
-    <t>Enter Company Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">ระบุชื่อบริษัท	</t>
   </si>
   <si>
@@ -1580,30 +1905,12 @@
     <t>patona-sellercenter-customerbook-modal-unsaved-title</t>
   </si>
   <si>
-    <t>You haven’t saved your data yet</t>
-  </si>
-  <si>
-    <t>คุณยังไม่ได้บันทึกข้อมูล</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-modal-unsaved-body-warning</t>
   </si>
   <si>
-    <t>You have not saved the data</t>
-  </si>
-  <si>
-    <t>คุณไม่ได้ทำการบันทึกข้อมูล</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-modal-unsaved-body-confirm</t>
   </si>
   <si>
-    <t>Do you want to leave this page?</t>
-  </si>
-  <si>
-    <t>ต้องการออกจากหน้านี้หรือไม่?</t>
-  </si>
-  <si>
     <t>patona-sellercenter-customerbook-toast-editcustomer-success</t>
   </si>
   <si>
@@ -1751,9 +2058,6 @@
     <t>patona-sellercenter-customerbook-shippingaddress-table-header-address</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
     <t>ที่อยู่</t>
   </si>
   <si>
@@ -1802,6 +2106,15 @@
     <t>แก้ไขข้อมูลลูกค้า</t>
   </si>
   <si>
+    <t>patona-sellercenter-customerbook-table-blank-nocustomer</t>
+  </si>
+  <si>
+    <t>No customer</t>
+  </si>
+  <si>
+    <t>ไม่มีรายชื่อลูกค้า</t>
+  </si>
+  <si>
     <t>patona-sellercenter-topbar-option-account</t>
   </si>
   <si>
@@ -1841,21 +2154,9 @@
     <t>patona-sellercenter-topbar-option-language</t>
   </si>
   <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>ภาษา</t>
-  </si>
-  <si>
     <t>patona-sellercenter-topbar-option-settings</t>
   </si>
   <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>ตั้งค่า</t>
-  </si>
-  <si>
     <t>patona-sellercenter-sidebar-radio-addnewstore</t>
   </si>
   <si>
@@ -1913,12 +2214,6 @@
     <t>patona-sellercenter-company-create-input-icon-company</t>
   </si>
   <si>
-    <t>Upload Company Logo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อัปโหลดโลโก้บริษัท	</t>
-  </si>
-  <si>
     <t>patona-sellercenter-company-create-input-description-company</t>
   </si>
   <si>
@@ -1946,9 +2241,6 @@
     <t>patona-sellercenter-company-create-input-placeholder-tax</t>
   </si>
   <si>
-    <t xml:space="preserve">Enter Tax ID </t>
-  </si>
-  <si>
     <t>patona-sellercenter-company-create-input-label-email</t>
   </si>
   <si>
@@ -1961,12 +2253,6 @@
     <t>patona-sellercenter-company-create-input-placeholder-email</t>
   </si>
   <si>
-    <t xml:space="preserve">Enter Company Email </t>
-  </si>
-  <si>
-    <t>ระบุอีเมลบริษัท</t>
-  </si>
-  <si>
     <t>patona-sellercenter-company-create-input-label-phone</t>
   </si>
   <si>
@@ -1979,9 +2265,6 @@
     <t>patona-sellercenter-company-create-input-placeholder-phone</t>
   </si>
   <si>
-    <t>Enter Primary Phone Number</t>
-  </si>
-  <si>
     <t xml:space="preserve">ระบุเบอร์โทรหลัก	</t>
   </si>
   <si>
@@ -1997,9 +2280,6 @@
     <t>patona-sellercenter-company-create-input-placeholder-subphone</t>
   </si>
   <si>
-    <t>Enter Secondary Phone Number</t>
-  </si>
-  <si>
     <t xml:space="preserve">ระบุเบอร์โทรสำรอง	</t>
   </si>
   <si>
@@ -2192,9 +2472,6 @@
     <t>patona-sellercenter-helper-text-error-minimum2</t>
   </si>
   <si>
-    <t>Please enter more than 2 characters</t>
-  </si>
-  <si>
     <t xml:space="preserve">กรุณาระบุมากกว่า 2 ตัวอักษรขึ้นไป        </t>
   </si>
   <si>
@@ -2303,21 +2580,9 @@
     <t>patona-sellercenter-helper-text-error-blankaddress</t>
   </si>
   <si>
-    <t>Please enter the address.</t>
-  </si>
-  <si>
-    <t>กรุณาระบุที่อยู่</t>
-  </si>
-  <si>
     <t>patona-sellercenter-helper-text-error-blankprimaryphone</t>
   </si>
   <si>
-    <t>Please enter the primary phone number.</t>
-  </si>
-  <si>
-    <t>กรุณาระบุเบอร์โทรหลัก</t>
-  </si>
-  <si>
     <t>patona-sellercenter-helper-text-error-blankbranchcode</t>
   </si>
   <si>
@@ -2333,9 +2598,6 @@
     <t>Please enter the company name.</t>
   </si>
   <si>
-    <t>กรุณาระบุชื่อบริษัท</t>
-  </si>
-  <si>
     <t>patona-sellercenter-helper-text-error-selectedcountry</t>
   </si>
   <si>
@@ -2348,21 +2610,9 @@
     <t>patona-sellercenter-helper-text-error-selectedpostalcode</t>
   </si>
   <si>
-    <t>Please select or enter the postal code</t>
-  </si>
-  <si>
-    <t>กรุณาเลือกหรือระบุรหัสไปรษณีย์</t>
-  </si>
-  <si>
     <t>patona-sellercenter-addressform-input-label-country</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>ประเทศ</t>
-  </si>
-  <si>
     <t>patona-sellercenter-addressform-input-placeholder-country</t>
   </si>
   <si>
@@ -2375,9 +2625,6 @@
     <t>patona-sellercenter-addressform-input-label-postalcode</t>
   </si>
   <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
     <t xml:space="preserve">รหัสไปรษณีย์  </t>
   </si>
   <si>
@@ -2447,13 +2694,7 @@
     <t>patona-sellercenter-addressform-input-label-address</t>
   </si>
   <si>
-    <t xml:space="preserve">ที่อยู่  </t>
-  </si>
-  <si>
     <t>patona-sellercenter-addressform-input-placeholder-address</t>
-  </si>
-  <si>
-    <t>Enter Addres</t>
   </si>
   <si>
     <t xml:space="preserve">ระบุที่อยู่	</t>
@@ -2588,7 +2829,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2612,6 +2853,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -2637,6 +2881,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -3583,9 +3831,15 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="A65" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2"/>
@@ -3656,6 +3910,387 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="47.0"/>
+    <col customWidth="1" min="2" max="2" width="32.13"/>
+    <col customWidth="1" min="3" max="3" width="24.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3663,6 +4298,474 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="38.75"/>
+    <col customWidth="1" min="2" max="2" width="32.63"/>
+    <col customWidth="1" min="3" max="3" width="39.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3687,54 +4790,54 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>178</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>180</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>182</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>299</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
@@ -3742,142 +4845,142 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>190</v>
+        <v>304</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>178</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>194</v>
+        <v>308</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>195</v>
+        <v>309</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>199</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>314</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>202</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>317</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>205</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>208</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>323</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>211</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>216</v>
+        <v>330</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>217</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>332</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>220</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>182</v>
+        <v>296</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>222</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>223</v>
+        <v>337</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>79</v>
@@ -3885,7 +4988,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>224</v>
+        <v>338</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>112</v>
@@ -3896,7 +4999,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>137</v>
@@ -3907,7 +5010,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>161</v>
@@ -3918,7 +5021,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>227</v>
+        <v>341</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>164</v>
@@ -3929,7 +5032,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>167</v>
@@ -3940,117 +5043,117 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>230</v>
+        <v>343</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>344</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>233</v>
+        <v>347</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>234</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>235</v>
+        <v>349</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>236</v>
+        <v>350</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>237</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>238</v>
+        <v>352</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>239</v>
+        <v>353</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>240</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>241</v>
+        <v>355</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>242</v>
+        <v>356</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>243</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>245</v>
+        <v>359</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>246</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>247</v>
+        <v>361</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>248</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>249</v>
+        <v>363</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>250</v>
+        <v>364</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>216</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>217</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>252</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>253</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>254</v>
+        <v>368</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>112</v>
@@ -4061,7 +5164,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>137</v>
@@ -4072,7 +5175,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>158</v>
@@ -4083,7 +5186,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>257</v>
+        <v>371</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>167</v>
@@ -4094,24 +5197,24 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>258</v>
+        <v>372</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>259</v>
+        <v>373</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>260</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>262</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>263</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4119,7 +5222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4144,7 +5247,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>378</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>34</v>
@@ -4155,65 +5258,65 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>265</v>
+        <v>379</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>266</v>
+        <v>380</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>267</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>268</v>
+        <v>382</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>269</v>
+        <v>383</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>271</v>
+        <v>385</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>272</v>
+        <v>386</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>273</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>274</v>
+        <v>388</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>275</v>
+        <v>389</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>276</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>277</v>
+        <v>391</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>278</v>
+        <v>392</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>279</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>281</v>
+        <v>395</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>56</v>
@@ -4221,32 +5324,32 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>283</v>
+        <v>397</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>284</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>399</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>252</v>
+        <v>366</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>253</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>56</v>
@@ -4254,7 +5357,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>287</v>
+        <v>401</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>37</v>
@@ -4265,10 +5368,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>288</v>
+        <v>402</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>289</v>
+        <v>403</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>60</v>
@@ -4276,10 +5379,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>404</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>291</v>
+        <v>405</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>175</v>
@@ -4287,29 +5390,29 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>292</v>
+        <v>406</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>293</v>
+        <v>407</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>294</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>295</v>
+        <v>409</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>296</v>
+        <v>410</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>297</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>298</v>
+        <v>412</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>52</v>
@@ -4320,40 +5423,40 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>300</v>
+        <v>414</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>301</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>302</v>
+        <v>416</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>303</v>
+        <v>417</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>304</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>305</v>
+        <v>419</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>306</v>
+        <v>420</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>307</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>308</v>
+        <v>422</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>112</v>
@@ -4364,10 +5467,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>309</v>
+        <v>423</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>310</v>
+        <v>424</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>119</v>
@@ -4375,10 +5478,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>126</v>
@@ -4386,7 +5489,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>313</v>
+        <v>427</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>137</v>
@@ -4397,7 +5500,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>167</v>
@@ -4408,7 +5511,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>315</v>
+        <v>429</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>143</v>
@@ -4419,7 +5522,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>149</v>
@@ -4430,7 +5533,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>161</v>
@@ -4441,7 +5544,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>318</v>
+        <v>432</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>164</v>
@@ -4452,29 +5555,29 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>319</v>
+        <v>433</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>321</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>322</v>
+        <v>436</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>323</v>
+        <v>437</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>324</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>109</v>
@@ -4485,7 +5588,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>326</v>
+        <v>440</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>128</v>
@@ -4496,7 +5599,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>327</v>
+        <v>441</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>131</v>
@@ -4507,84 +5610,84 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>329</v>
+        <v>443</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>330</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>331</v>
+        <v>445</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>332</v>
+        <v>446</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>333</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>334</v>
+        <v>448</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>335</v>
+        <v>449</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>336</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>337</v>
+        <v>451</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>338</v>
+        <v>452</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>339</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>340</v>
+        <v>454</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>296</v>
+        <v>410</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>297</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>341</v>
+        <v>455</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>343</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>344</v>
+        <v>458</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>345</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>460</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>78</v>
@@ -4595,57 +5698,68 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>349</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>350</v>
+        <v>464</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>352</v>
+        <v>466</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>353</v>
+        <v>467</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>354</v>
+        <v>468</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>355</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>356</v>
+        <v>470</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>357</v>
+        <v>471</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>358</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="s">
-        <v>359</v>
+      <c r="A47" s="10" t="s">
+        <v>473</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4653,7 +5767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4678,326 +5792,326 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>360</v>
+        <v>475</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>361</v>
+        <v>476</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>362</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>363</v>
+        <v>478</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>364</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>365</v>
+        <v>480</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>366</v>
+        <v>481</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>367</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>368</v>
+        <v>483</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>369</v>
+        <v>484</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>370</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>371</v>
+        <v>486</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>372</v>
+        <v>487</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>373</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>374</v>
+        <v>489</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>375</v>
+        <v>490</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>376</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>492</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>378</v>
+        <v>493</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>379</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>380</v>
+        <v>495</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>381</v>
+        <v>496</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>382</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>383</v>
+        <v>498</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>384</v>
+        <v>499</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>385</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>386</v>
+        <v>501</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>387</v>
+        <v>502</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>388</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>389</v>
+        <v>504</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>381</v>
+        <v>496</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>382</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>390</v>
+        <v>505</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>283</v>
+        <v>397</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>392</v>
+        <v>507</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>393</v>
+        <v>508</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>394</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>395</v>
+        <v>510</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>396</v>
+        <v>511</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>398</v>
+        <v>513</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>399</v>
+        <v>514</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>400</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>401</v>
+        <v>516</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>402</v>
+        <v>517</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>403</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>404</v>
+        <v>519</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>366</v>
+        <v>481</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>406</v>
+        <v>521</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>407</v>
+        <v>522</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>408</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>409</v>
+        <v>524</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>410</v>
+        <v>525</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>411</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>412</v>
+        <v>527</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>414</v>
+        <v>529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>415</v>
+        <v>530</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>417</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>418</v>
+        <v>533</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>419</v>
+        <v>534</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>420</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>421</v>
+        <v>536</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>422</v>
+        <v>537</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>423</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>424</v>
+        <v>539</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>422</v>
+        <v>537</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>423</v>
+        <v>538</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>425</v>
+        <v>540</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>427</v>
+        <v>542</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>428</v>
+        <v>543</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>429</v>
+        <v>544</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>430</v>
+        <v>545</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>431</v>
+        <v>546</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>429</v>
+        <v>544</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>430</v>
+        <v>545</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>432</v>
+        <v>547</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>433</v>
+        <v>548</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>434</v>
+        <v>549</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>435</v>
+        <v>550</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>436</v>
+        <v>551</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>437</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>78</v>
@@ -5008,675 +6122,681 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>439</v>
+        <v>554</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>441</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>442</v>
+        <v>555</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>443</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>444</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>445</v>
+        <v>556</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>446</v>
+        <v>557</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>447</v>
+        <v>558</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>448</v>
+        <v>559</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>449</v>
+        <v>493</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
-        <v>450</v>
+        <v>561</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>447</v>
+        <v>557</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>451</v>
+        <v>562</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>452</v>
+        <v>563</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>453</v>
+        <v>564</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>454</v>
+        <v>565</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>455</v>
+        <v>566</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>456</v>
+        <v>567</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>457</v>
+        <v>568</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>458</v>
+        <v>569</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>459</v>
+        <v>570</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>460</v>
+        <v>571</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>417</v>
+        <v>532</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>461</v>
+        <v>572</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>387</v>
+        <v>502</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>388</v>
+        <v>503</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>462</v>
+        <v>573</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>464</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>465</v>
+        <v>576</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>466</v>
+        <v>577</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>467</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>468</v>
+        <v>579</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>366</v>
+        <v>481</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>469</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>470</v>
+        <v>581</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>407</v>
+        <v>522</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>408</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>471</v>
+        <v>582</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>472</v>
+        <v>583</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>473</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>474</v>
+        <v>585</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>475</v>
+        <v>586</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>476</v>
+        <v>587</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>477</v>
+        <v>588</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>464</v>
+        <v>575</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>478</v>
+        <v>589</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>466</v>
+        <v>577</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>467</v>
+        <v>578</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>479</v>
+        <v>590</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>480</v>
+        <v>591</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>481</v>
+        <v>592</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>482</v>
+        <v>593</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>483</v>
+        <v>594</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>484</v>
+        <v>595</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>485</v>
+        <v>596</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>366</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>469</v>
+        <v>580</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>486</v>
+        <v>597</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>407</v>
+        <v>522</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>408</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>487</v>
+        <v>598</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>488</v>
+        <v>599</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>489</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>490</v>
+        <v>601</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>414</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>491</v>
+        <v>602</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>492</v>
+        <v>199</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>493</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>494</v>
+        <v>603</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>495</v>
+        <v>212</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>497</v>
+        <v>605</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>498</v>
+        <v>606</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>499</v>
+        <v>607</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>500</v>
+        <v>608</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>501</v>
+        <v>609</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>502</v>
+        <v>610</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>503</v>
+        <v>611</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>504</v>
+        <v>612</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>505</v>
+        <v>613</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>506</v>
+        <v>614</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>508</v>
+        <v>616</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>509</v>
+        <v>617</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>510</v>
+        <v>618</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>511</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>513</v>
+        <v>621</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>514</v>
+        <v>622</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>515</v>
+        <v>623</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>516</v>
+        <v>237</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>517</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>518</v>
+        <v>624</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>519</v>
+        <v>247</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>520</v>
+        <v>248</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>521</v>
+        <v>625</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>522</v>
+        <v>250</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>523</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>524</v>
+        <v>626</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>525</v>
+        <v>627</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>526</v>
+        <v>628</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>527</v>
+        <v>629</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>528</v>
+        <v>630</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>530</v>
+        <v>632</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>531</v>
+        <v>633</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>532</v>
+        <v>634</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>533</v>
+        <v>635</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>534</v>
+        <v>636</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>535</v>
+        <v>637</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>536</v>
+        <v>638</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>537</v>
+        <v>639</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>538</v>
+        <v>640</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>539</v>
+        <v>641</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>540</v>
+        <v>642</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>541</v>
+        <v>643</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>542</v>
+        <v>644</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>543</v>
+        <v>645</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>544</v>
+        <v>646</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>545</v>
+        <v>647</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>546</v>
+        <v>648</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>547</v>
+        <v>649</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>548</v>
+        <v>650</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>549</v>
+        <v>651</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>550</v>
+        <v>652</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>551</v>
+        <v>653</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>552</v>
+        <v>654</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>553</v>
+        <v>655</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>555</v>
+        <v>657</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>556</v>
+        <v>658</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>557</v>
+        <v>659</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>558</v>
+        <v>660</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>559</v>
+        <v>661</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>560</v>
+        <v>662</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>561</v>
+        <v>663</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>562</v>
+        <v>664</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>563</v>
+        <v>665</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>564</v>
+        <v>666</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>565</v>
+        <v>667</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>566</v>
+        <v>668</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>567</v>
+        <v>669</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>568</v>
+        <v>670</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>569</v>
+        <v>671</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>570</v>
+        <v>672</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>571</v>
+        <v>673</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>366</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>367</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>572</v>
+        <v>674</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>573</v>
+        <v>285</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>574</v>
+        <v>675</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>575</v>
+        <v>676</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>576</v>
+        <v>677</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>577</v>
+        <v>678</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>578</v>
+        <v>679</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>579</v>
+        <v>680</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>580</v>
+        <v>681</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>581</v>
+        <v>682</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>582</v>
+        <v>683</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>394</v>
+        <v>509</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>583</v>
+        <v>684</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>584</v>
+        <v>685</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>481</v>
+        <v>592</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>585</v>
+        <v>686</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>488</v>
+        <v>599</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>489</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>586</v>
+        <v>687</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>573</v>
+        <v>285</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>574</v>
+        <v>675</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>587</v>
+        <v>688</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>589</v>
+        <v>689</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="A92" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>693</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5701,90 +6821,90 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>590</v>
+        <v>694</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>591</v>
+        <v>695</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>592</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="s">
-        <v>593</v>
+        <v>697</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>594</v>
+        <v>698</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>595</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>596</v>
+        <v>700</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>597</v>
+        <v>701</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>598</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>599</v>
+        <v>703</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>600</v>
+        <v>704</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>601</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>602</v>
+        <v>706</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>603</v>
+        <v>282</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>604</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>605</v>
+        <v>707</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>606</v>
+        <v>279</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>607</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>608</v>
+        <v>708</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>609</v>
+        <v>709</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>610</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>611</v>
+        <v>711</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>612</v>
+        <v>712</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>613</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>
@@ -5792,7 +6912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5817,194 +6937,194 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>614</v>
+        <v>714</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>615</v>
+        <v>715</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>616</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>617</v>
+        <v>717</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>618</v>
+        <v>718</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>619</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>620</v>
+        <v>720</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>621</v>
+        <v>721</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>622</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>623</v>
+        <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>624</v>
+        <v>724</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>625</v>
+        <v>725</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>626</v>
+        <v>726</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>627</v>
+        <v>187</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>628</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>630</v>
+        <v>728</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>631</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>632</v>
+        <v>730</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>492</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>633</v>
+        <v>731</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>634</v>
+        <v>732</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>495</v>
+        <v>212</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>635</v>
+        <v>733</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>480</v>
+        <v>591</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>636</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>637</v>
+        <v>735</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>638</v>
+        <v>215</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>484</v>
+        <v>595</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>639</v>
+        <v>736</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>640</v>
+        <v>737</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>641</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>642</v>
+        <v>739</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>643</v>
+        <v>218</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>644</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>645</v>
+        <v>740</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>647</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>648</v>
+        <v>743</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>649</v>
+        <v>221</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>650</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>651</v>
+        <v>745</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>652</v>
+        <v>746</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>653</v>
+        <v>747</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>654</v>
+        <v>748</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>655</v>
+        <v>224</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>656</v>
+        <v>749</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>657</v>
+        <v>750</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>658</v>
+        <v>751</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>659</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>660</v>
+        <v>753</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>78</v>
@@ -6015,62 +7135,62 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>661</v>
+        <v>754</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>662</v>
+        <v>755</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>663</v>
+        <v>756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>664</v>
+        <v>757</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>665</v>
+        <v>758</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>666</v>
+        <v>759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>667</v>
+        <v>760</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>668</v>
+        <v>761</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>669</v>
+        <v>762</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>670</v>
+        <v>763</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>671</v>
+        <v>764</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>672</v>
+        <v>765</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>673</v>
+        <v>766</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>674</v>
+        <v>767</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>675</v>
+        <v>768</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>676</v>
+        <v>769</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>128</v>
@@ -6081,13 +7201,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>677</v>
+        <v>770</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>678</v>
+        <v>771</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>679</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -6095,7 +7215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6108,7 +7228,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -6120,150 +7240,150 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>680</v>
+        <v>773</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>681</v>
+        <v>774</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>682</v>
+        <v>775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>683</v>
+        <v>776</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>684</v>
+        <v>777</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>685</v>
+        <v>778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>686</v>
+        <v>779</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>687</v>
+        <v>780</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>688</v>
+        <v>781</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>689</v>
+        <v>782</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>690</v>
+        <v>783</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>691</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>692</v>
+        <v>785</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>693</v>
+        <v>786</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>694</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>695</v>
+        <v>788</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>696</v>
+        <v>789</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>697</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>698</v>
+        <v>791</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>699</v>
+        <v>792</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>700</v>
+        <v>793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>701</v>
+        <v>794</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>795</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>703</v>
+        <v>796</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>704</v>
+        <v>797</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>647</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>705</v>
+        <v>798</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>649</v>
+        <v>221</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>650</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>706</v>
+        <v>799</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>652</v>
+        <v>746</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>653</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>707</v>
+        <v>800</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>655</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>656</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>708</v>
+        <v>801</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>709</v>
+        <v>802</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>710</v>
+        <v>803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>711</v>
+        <v>804</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>78</v>
@@ -6274,35 +7394,35 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>712</v>
+        <v>805</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>713</v>
+        <v>806</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>714</v>
+        <v>807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>715</v>
+        <v>808</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>716</v>
+        <v>809</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>717</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>718</v>
+        <v>811</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>671</v>
+        <v>764</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>672</v>
+        <v>765</v>
       </c>
     </row>
     <row r="19">
@@ -6345,7 +7465,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6370,32 +7490,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>719</v>
+        <v>812</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>720</v>
+        <v>259</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>721</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>722</v>
+        <v>814</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>723</v>
+        <v>815</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>724</v>
+        <v>816</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>725</v>
+        <v>817</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>156</v>
@@ -6403,560 +7523,179 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>727</v>
+        <v>819</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>728</v>
+        <v>820</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>729</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>730</v>
+        <v>822</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>731</v>
+        <v>823</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>732</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>733</v>
+        <v>825</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>734</v>
+        <v>826</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>735</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>736</v>
+        <v>828</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>737</v>
+        <v>829</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>738</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>739</v>
+        <v>831</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>728</v>
+        <v>820</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>740</v>
+        <v>832</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>741</v>
+        <v>833</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>742</v>
+        <v>834</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>743</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>744</v>
+        <v>836</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>746</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>747</v>
+        <v>839</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>749</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>750</v>
+        <v>842</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>751</v>
+        <v>843</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>752</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>753</v>
+        <v>845</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>754</v>
+        <v>846</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>755</v>
+        <v>847</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>756</v>
+        <v>848</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>757</v>
+        <v>273</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>758</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>759</v>
+        <v>849</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>760</v>
+        <v>267</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>761</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>762</v>
+        <v>850</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>763</v>
+        <v>851</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>764</v>
+        <v>852</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>765</v>
+        <v>853</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>766</v>
+        <v>854</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>767</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>768</v>
+        <v>855</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>769</v>
+        <v>856</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>770</v>
+        <v>857</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>771</v>
+        <v>858</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>772</v>
+        <v>270</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="47.0"/>
-    <col customWidth="1" min="2" max="2" width="32.13"/>
-    <col customWidth="1" min="3" max="3" width="24.63"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>816</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>818</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+        <v>271</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
